--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>92609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B6" t="n">
-        <v>79004</v>
+        <v>92609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R6" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B7" t="n">
-        <v>92535</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R7" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>92609</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R3" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>92615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R4" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
         <v>127128174</v>
       </c>
       <c r="B6" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127128170</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R3" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R4" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>92615</v>
+        <v>79038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R6" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>79038</v>
+        <v>92616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R7" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B6" t="n">
-        <v>79038</v>
+        <v>92616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R6" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B7" t="n">
-        <v>92616</v>
+        <v>79038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R7" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>92616</v>
+        <v>79042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R6" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>79038</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R7" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R3" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R4" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R3" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R4" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R3" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R4" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>92628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R6" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R7" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>79047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R6" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1188,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R7" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92639</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,14 +1088,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79053</v>
+        <v>79144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,14 +1189,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92639</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,14 +1290,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92631</v>
+        <v>92786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1391,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128168</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79063</v>
+        <v>79065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79065</v>
+        <v>79067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128172</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>79067</v>
+        <v>79068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127128169</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B6" t="n">
-        <v>79068</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R6" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>79068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R7" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128173</v>
+        <v>127128171</v>
       </c>
       <c r="B3" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764518</v>
+        <v>764540</v>
       </c>
       <c r="R3" t="n">
-        <v>7173301</v>
+        <v>7173089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R4" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128174</v>
+        <v>127128170</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>79068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764724</v>
+        <v>764484</v>
       </c>
       <c r="R6" t="n">
-        <v>7173036</v>
+        <v>7173149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128170</v>
+        <v>127128174</v>
       </c>
       <c r="B7" t="n">
-        <v>79068</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764484</v>
+        <v>764724</v>
       </c>
       <c r="R7" t="n">
-        <v>7173149</v>
+        <v>7173036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128172</v>
+        <v>127128169</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>764482</v>
+        <v>764474</v>
       </c>
       <c r="R2" t="n">
-        <v>7173152</v>
+        <v>7173153</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128171</v>
+        <v>127128173</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764540</v>
+        <v>764518</v>
       </c>
       <c r="R3" t="n">
-        <v>7173089</v>
+        <v>7173301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,14 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128173</v>
+        <v>127128174</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764518</v>
+        <v>764724</v>
       </c>
       <c r="R4" t="n">
-        <v>7173301</v>
+        <v>7173036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128168</v>
+        <v>133103637</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,35 +989,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1025,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>764600</v>
+        <v>764627</v>
       </c>
       <c r="R5" t="n">
-        <v>7173217</v>
+        <v>7172893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,17 +1050,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lock 2st</t>
+          <t>fjolårets fruktkropp med vit mycelmatta under.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,54 +1069,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128170</v>
+        <v>127128171</v>
       </c>
       <c r="B6" t="n">
-        <v>79068</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764484</v>
+        <v>764540</v>
       </c>
       <c r="R6" t="n">
-        <v>7173149</v>
+        <v>7173089</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128174</v>
+        <v>127128172</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764724</v>
+        <v>764482</v>
       </c>
       <c r="R7" t="n">
-        <v>7173036</v>
+        <v>7173152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,45 +1290,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128169</v>
+        <v>133103530</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ljusheden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>764474</v>
+        <v>764452</v>
       </c>
       <c r="R8" t="n">
-        <v>7173153</v>
+        <v>7173319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,32 +1376,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133103958</v>
+        <v>133103565</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,31 +1406,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>764668</v>
+        <v>764420</v>
       </c>
       <c r="R9" t="n">
-        <v>7173078</v>
+        <v>7173214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,11 +1473,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ett tiotal bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,32 +1500,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133103656</v>
+        <v>133103681</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>764739</v>
+        <v>764819</v>
       </c>
       <c r="R10" t="n">
-        <v>7172981</v>
+        <v>7173069</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,42 +1605,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133103925</v>
+        <v>133104019</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1658,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>764674</v>
+        <v>764529</v>
       </c>
       <c r="R11" t="n">
-        <v>7173074</v>
+        <v>7173286</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,17 +1685,13 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>barksprätt på död gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1725,52 +1710,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133104019</v>
+        <v>127128170</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ljusheden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>764529</v>
+        <v>764484</v>
       </c>
       <c r="R12" t="n">
-        <v>7173286</v>
+        <v>7173149</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,12 +1775,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,51 +1789,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133103565</v>
+        <v>133103656</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>764420</v>
+        <v>764739</v>
       </c>
       <c r="R13" t="n">
-        <v>7173214</v>
+        <v>7172981</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133103530</v>
+        <v>133103925</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,30 +1927,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1977,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>764452</v>
+        <v>764674</v>
       </c>
       <c r="R14" t="n">
-        <v>7173319</v>
+        <v>7173074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,13 +1997,17 @@
           <t>2026-05-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>barksprätt på död gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133103681</v>
+        <v>127128168</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,30 +2037,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2082,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>764819</v>
+        <v>764600</v>
       </c>
       <c r="R15" t="n">
-        <v>7173069</v>
+        <v>7173217</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,12 +2103,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lock 2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,22 +2122,136 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133103958</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ljusheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>764668</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7173078</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ett tiotal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29693-2025 artfynd.xlsx
+++ b/artfynd/A 29693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128169</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103637</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128172</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103530</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103565</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133104019</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128170</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,6 +1973,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103656</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103925</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128168</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2252,8 +2327,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133103958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>